--- a/method_comparison.xlsx
+++ b/method_comparison.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hygrometer" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thermometer" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Barometer" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Hygrometer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Thermometer" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Barometer" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -47,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,37 +419,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Pair</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TabPFN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Linear</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>kNN</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>XGBoost</t>
         </is>
@@ -477,16 +465,16 @@
         <v>775</v>
       </c>
       <c r="C2" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="D2" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="F2" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="G2" t="n">
         <v>1.05</v>
@@ -533,13 +521,13 @@
         <v>1.7</v>
       </c>
       <c r="E4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="F4" t="n">
         <v>1.26</v>
       </c>
       <c r="G4" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="5">
@@ -549,22 +537,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1006</v>
+        <v>984</v>
       </c>
       <c r="C5" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="E5" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="F5" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="G5" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="6">
@@ -611,7 +599,7 @@
         <v>1.42</v>
       </c>
       <c r="F7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G7" t="n">
         <v>1.36</v>
@@ -658,13 +646,13 @@
         <v>1.87</v>
       </c>
       <c r="E9" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="F9" t="n">
         <v>1.55</v>
       </c>
       <c r="G9" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="10">
@@ -674,22 +662,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1193</v>
+        <v>1171</v>
       </c>
       <c r="C10" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="D10" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="E10" t="n">
         <v>1.5</v>
       </c>
       <c r="F10" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="G10" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="11">
@@ -699,22 +687,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2199</v>
+        <v>2173</v>
       </c>
       <c r="C11" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="D11" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="E11" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="G11" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="12">
@@ -932,37 +920,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Pair</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TabPFN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Linear</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>kNN</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>XGBoost</t>
         </is>
@@ -981,10 +969,10 @@
         <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>51.2</v>
+        <v>49</v>
       </c>
       <c r="E2" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="F2" t="n">
         <v>28</v>
@@ -1000,22 +988,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1006</v>
+        <v>984</v>
       </c>
       <c r="C3" t="n">
-        <v>23.6</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>51.7</v>
+        <v>51</v>
       </c>
       <c r="E3" t="n">
-        <v>34.6</v>
+        <v>36</v>
       </c>
       <c r="F3" t="n">
-        <v>33.7</v>
+        <v>34</v>
       </c>
       <c r="G3" t="n">
-        <v>30.4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -1028,19 +1016,19 @@
         <v>765</v>
       </c>
       <c r="C4" t="n">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="E4" t="n">
-        <v>36.1</v>
+        <v>37</v>
       </c>
       <c r="F4" t="n">
-        <v>37.3</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
-        <v>33.6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -1053,10 +1041,10 @@
         <v>497</v>
       </c>
       <c r="C5" t="n">
-        <v>26.4</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>66.7</v>
+        <v>67</v>
       </c>
       <c r="E5" t="n">
         <v>37</v>
@@ -1065,7 +1053,7 @@
         <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>34.5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
@@ -1078,19 +1066,19 @@
         <v>751</v>
       </c>
       <c r="C6" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="D6" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
       <c r="E6" t="n">
-        <v>34.8</v>
+        <v>35</v>
       </c>
       <c r="F6" t="n">
-        <v>34.7</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>31.6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -1103,19 +1091,19 @@
         <v>487</v>
       </c>
       <c r="C7" t="n">
-        <v>27.2</v>
+        <v>27</v>
       </c>
       <c r="D7" t="n">
-        <v>58.5</v>
+        <v>58</v>
       </c>
       <c r="E7" t="n">
-        <v>41.4</v>
+        <v>41</v>
       </c>
       <c r="F7" t="n">
-        <v>40.2</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8">
@@ -1128,19 +1116,19 @@
         <v>284</v>
       </c>
       <c r="C8" t="n">
-        <v>28.3</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
-        <v>50.6</v>
+        <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>41.3</v>
+        <v>42</v>
       </c>
       <c r="F8" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>35.4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
@@ -1150,22 +1138,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1193</v>
+        <v>1171</v>
       </c>
       <c r="C9" t="n">
-        <v>32.3</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E9" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F9" t="n">
-        <v>40.6</v>
+        <v>41</v>
       </c>
       <c r="G9" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -1200,22 +1188,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2199</v>
+        <v>2173</v>
       </c>
       <c r="C11" t="n">
-        <v>33.4</v>
+        <v>34</v>
       </c>
       <c r="D11" t="n">
         <v>60</v>
       </c>
       <c r="E11" t="n">
-        <v>43.7</v>
+        <v>45</v>
       </c>
       <c r="F11" t="n">
-        <v>44.1</v>
+        <v>45</v>
       </c>
       <c r="G11" t="n">
-        <v>40.9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
@@ -1228,19 +1216,19 @@
         <v>537</v>
       </c>
       <c r="C12" t="n">
-        <v>35.7</v>
+        <v>36</v>
       </c>
       <c r="D12" t="n">
-        <v>73.3</v>
+        <v>73</v>
       </c>
       <c r="E12" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>45.7</v>
+        <v>46</v>
       </c>
       <c r="G12" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -1281,16 +1269,16 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>65.5</v>
+        <v>65</v>
       </c>
       <c r="E14" t="n">
-        <v>53.4</v>
+        <v>53</v>
       </c>
       <c r="F14" t="n">
-        <v>50.3</v>
+        <v>50</v>
       </c>
       <c r="G14" t="n">
-        <v>49.4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
@@ -1303,19 +1291,19 @@
         <v>208</v>
       </c>
       <c r="C15" t="n">
-        <v>48.5</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
       </c>
       <c r="E15" t="n">
-        <v>63.3</v>
+        <v>63</v>
       </c>
       <c r="F15" t="n">
-        <v>63.1</v>
+        <v>63</v>
       </c>
       <c r="G15" t="n">
-        <v>61.8</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1433,37 +1421,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Pair</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TabPFN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Linear</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>kNN</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>XGBoost</t>
         </is>
@@ -1504,19 +1492,19 @@
         <v>775</v>
       </c>
       <c r="C3" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="D3" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="E3" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="F3" t="n">
         <v>2.14</v>
       </c>
       <c r="G3" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="4">
@@ -1529,19 +1517,19 @@
         <v>751</v>
       </c>
       <c r="C4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="E4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="F4" t="n">
         <v>1.98</v>
       </c>
       <c r="G4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="5">
@@ -1604,19 +1592,19 @@
         <v>284</v>
       </c>
       <c r="C7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="D7" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="E7" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="F7" t="n">
         <v>1.94</v>
       </c>
       <c r="G7" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="8">
@@ -1685,13 +1673,13 @@
         <v>2.96</v>
       </c>
       <c r="E10" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="F10" t="n">
         <v>2.48</v>
       </c>
       <c r="G10" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="11">
@@ -1726,22 +1714,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1006</v>
+        <v>984</v>
       </c>
       <c r="C12" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="D12" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="E12" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="F12" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="G12" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="13">
@@ -1776,22 +1764,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1193</v>
+        <v>1171</v>
       </c>
       <c r="C14" t="n">
         <v>1.98</v>
       </c>
       <c r="D14" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="F14" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="G14" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="15">
@@ -1826,22 +1814,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2199</v>
+        <v>2173</v>
       </c>
       <c r="C16" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="D16" t="n">
-        <v>3.97</v>
+        <v>3.92</v>
       </c>
       <c r="E16" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="F16" t="n">
         <v>3.05</v>
       </c>
       <c r="G16" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="17">
